--- a/docs/成本管理.xlsx
+++ b/docs/成本管理.xlsx
@@ -46,7 +46,7 @@
     <t>token消耗</t>
   </si>
   <si>
-    <t>5元</t>
+    <t>15元</t>
   </si>
 </sst>
 </file>
@@ -984,7 +984,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="17.5454545454545" customWidth="1"/>
-    <col min="2" max="2" width="9.6" customWidth="1"/>
+    <col min="2" max="2" width="13.0727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">

--- a/docs/成本管理.xlsx
+++ b/docs/成本管理.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FullStack\finding\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>成本</t>
   </si>
@@ -40,13 +45,16 @@
     <t>购买云服务器</t>
   </si>
   <si>
+    <t>38元</t>
+  </si>
+  <si>
     <t>购买域名</t>
   </si>
   <si>
     <t>token消耗</t>
   </si>
   <si>
-    <t>15元</t>
+    <t>40元</t>
   </si>
 </sst>
 </file>
@@ -999,20 +1007,22 @@
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1"/>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/docs/成本管理.xlsx
+++ b/docs/成本管理.xlsx
@@ -45,7 +45,7 @@
     <t>购买云服务器</t>
   </si>
   <si>
-    <t>38元</t>
+    <t>109元</t>
   </si>
   <si>
     <t>购买域名</t>
